--- a/outputs/jackson-county-industrial-intelligence/Jackson_County_I85_Industrial_Entitlement_Landscape.xlsx
+++ b/outputs/jackson-county-industrial-intelligence/Jackson_County_I85_Industrial_Entitlement_Landscape.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R92813489ae2d4bd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent Cases" sheetId="2" r:id="R637d5906802043f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Matrix" sheetId="3" r:id="Reb6bb30191414756"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Players" sheetId="4" r:id="R19ebc6ba460a4f9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Audit" sheetId="5" r:id="Re960fce86c734c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R6116d344d9ff4ac1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent Cases" sheetId="2" r:id="Re12f68b586fb4fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Matrix" sheetId="3" r:id="R6e2b12cd58a74c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conversion Matrix" sheetId="4" r:id="R047eac7bff254c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Players" sheetId="5" r:id="R492f781da0574995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Audit" sheetId="6" r:id="Rb2bd41411dc04f0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +473,7 @@
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="25" t="str">
-        <x:v>Investment read: Jackson County remains industrial-friendly inside established I-85, US 129, and Commerce/US 441 nodes, but the evidence standard is now deliberately split between DRI/regional review and final local action. The strongest verified local approvals are Wayne Poultry FLUM conversion, Ingram GI, Tom White/EastGroup LI, Valentine GI, Jackson Quarry HI/SUP, and Commerce Taylor &amp; Mathis M-1 distribution/truck-terminal approvals. Whoville is coded as withdrawn without prejudice. Jefferson, Pendergrass, and several newer county DRI rows still need signed final records before being treated as full entitlement comps.</x:v>
+        <x:v>Broker read: Jackson County has a real industrial-conversion lane, but it is node-driven. Green/yellow opportunities start with existing industrial zoning, industrial FLUM, urban character areas, arterial access, utilities, and a clear buffer/traffic story. Orange/red opportunities are rural, conservation, residential-plan, truck-heavy, or heavy-industrial edge cases that need a larger entitlement discount.</x:v>
       </x:c>
       <x:c r="B4" s="26"/>
       <x:c r="C4" s="26"/>
@@ -504,79 +505,79 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="36" t="str">
-        <x:v>Closed Local Evidence</x:v>
+        <x:v>Green / Yellow Targets</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>Useful DRI / Market Signals</x:v>
+        <x:v>Orange / Red Targets</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>Highest Priority Gaps</x:v>
+        <x:v>Customer Rule</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="39" t="str">
-        <x:v>Wayne Poultry: four FLUM map amendments approved 4-0</x:v>
+        <x:v>Existing LI/GI/HI or city M-1/M-2 inside I-85/US 129/Commerce nodes</x:v>
       </x:c>
       <x:c r="B9" s="39" t="str">
-        <x:v>Project Orchid: DRI plus official water-use correction</x:v>
+        <x:v>Agricultural/conservation/residential-plan areas creating a new industrial edge</x:v>
       </x:c>
       <x:c r="C9" s="39" t="str">
-        <x:v>Jefferson final actions: Orchid, Rush, RaceTrac, Concord, Hog Mountain</x:v>
+        <x:v>Buy the node, not just the acreage.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="39" t="str">
-        <x:v>Ingram: A-2 to GI approved 4-0 with buffer/UDC conditions</x:v>
+        <x:v>A-2 to LI/GI where the site completes an existing industrial pattern</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Choice Equipment: A-2 to GI / Urban / Industrial request verified in DRI</x:v>
+        <x:v>Truck stops, drop lots, diesel, or heavy repair outside proven truck nodes</x:v>
       </x:c>
       <x:c r="C10" s="39" t="str">
-        <x:v>County final actions: Choice, 7-Eleven/Peterbilt, Hwy 124/Maddox, East Jackson Quarry</x:v>
+        <x:v>Price truck intensity separately from warehouse zoning.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="39" t="str">
-        <x:v>Tom White/EastGroup: A-2 to LI approved 4-0 with road/buffer conditions</x:v>
+        <x:v>Commercial or highway frontage converting to LI/M-1 at a proven industrial corridor</x:v>
       </x:c>
       <x:c r="B11" s="39" t="str">
-        <x:v>Jackson 85 North: phase-one delivery verified by developer/market sources</x:v>
+        <x:v>HI/quarry/heavy industrial unless the customer has a special-use thesis</x:v>
       </x:c>
       <x:c r="C11" s="39" t="str">
-        <x:v>Pendergrass entitlement chain: Jackson 85 North, Jackson Farms, Project Fortune</x:v>
+        <x:v>Treat conditions as capex, not paperwork.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="39" t="str">
-        <x:v>Valentine: RZ-22-0122/0123 A-2 to GI approved 3-0 with road/buffer conditions</x:v>
+        <x:v>Annexation to Commerce/Jefferson/Pendergrass where utilities and city plan support industrial</x:v>
       </x:c>
       <x:c r="B12" s="39" t="str">
-        <x:v>Rush and Concord: official Jefferson packets found, final signed records still open</x:v>
+        <x:v>DRI-only or market-only projects without local ordinance/site-plan support</x:v>
       </x:c>
       <x:c r="C12" s="39" t="str">
-        <x:v>Jefferson signed final records: Orchid, Rush, RaceTrac, Concord, Hog Mountain</x:v>
+        <x:v>Require local action before treating a comp as bankable.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="39" t="str">
-        <x:v>Whoville: withdrawn without prejudice accepted 5-0 after staff/PC denial posture</x:v>
+        <x:v>Wayne Poultry, Valentine, Tom White/EastGroup, Ingram, Taylor &amp; Mathis</x:v>
       </x:c>
       <x:c r="B13" s="39" t="str">
-        <x:v>Project Orchid: Jefferson PC packet found for R-26-J03/CU-26-J02/V-26-J06</x:v>
+        <x:v>Whoville, Hwy 124/Maddox, East Jackson Quarry</x:v>
       </x:c>
       <x:c r="C13" s="39" t="str">
-        <x:v>Current development status and parcel-level zoning confirmations</x:v>
+        <x:v>The most valuable screen is FLUM + road + utility + neighbor fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="39" t="str">
-        <x:v>Commerce Taylor &amp; Mathis: annexation, M-1 rezoning, and CUP approved unanimously</x:v>
+        <x:v>Conditional LI/GI parcels where only operating conditions need work</x:v>
       </x:c>
       <x:c r="B14" s="39" t="str">
-        <x:v>Hwy 124 and East Jackson Quarry: adverse DRI plan-compatibility signals</x:v>
+        <x:v>Cheap rural land with weak access or residential adjacency</x:v>
       </x:c>
       <x:c r="C14" s="39" t="str">
-        <x:v>RaceTrac permit/local action and Pendergrass municipal records</x:v>
+        <x:v>Entitlement discount should widen fast outside the industrial fabric.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2450,1306 +2451,268 @@
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="44" t="str">
-        <x:v>name</x:v>
+        <x:v>conversion_rating</x:v>
       </x:c>
       <x:c r="B1" s="44" t="str">
-        <x:v>role</x:v>
+        <x:v>starting_zoning_or_status</x:v>
       </x:c>
       <x:c r="C1" s="44" t="str">
-        <x:v>organization</x:v>
+        <x:v>starting_flum_character_area</x:v>
       </x:c>
       <x:c r="D1" s="44" t="str">
-        <x:v>jurisdiction_or_case</x:v>
+        <x:v>target_zoning_or_use</x:v>
       </x:c>
       <x:c r="E1" s="44" t="str">
-        <x:v>player_type</x:v>
+        <x:v>customer_read</x:v>
       </x:c>
       <x:c r="F1" s="44" t="str">
-        <x:v>evidence_based_signal</x:v>
+        <x:v>case_examples</x:v>
       </x:c>
       <x:c r="G1" s="44" t="str">
-        <x:v>source_url</x:v>
+        <x:v>conditions_or_friction</x:v>
       </x:c>
       <x:c r="H1" s="44" t="str">
-        <x:v>confidence</x:v>
+        <x:v>acquisition_rule</x:v>
+      </x:c>
+      <x:c r="I1" s="44" t="str">
+        <x:v>primary_source_ids</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="39" t="str">
-        <x:v>Marty Clark</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="B2" s="39" t="str">
-        <x:v>Chairman</x:v>
+        <x:v>Existing LI/GI/HI or conditional industrial zoning inside an established node</x:v>
       </x:c>
       <x:c r="C2" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Industrial or Urban / industrial-supportive character area</x:v>
       </x:c>
       <x:c r="D2" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>Industrial use confirmation condition modification CUP variance or site-plan execution</x:v>
       </x:c>
       <x:c r="E2" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Best customer starting point because the public question is usually operations conditions traffic buffers or utilities rather than whether industrial belongs there</x:v>
       </x:c>
       <x:c r="F2" s="39" t="str">
-        <x:v>At-large chair of the legislative body for county zoning; former Planning Commission chair</x:v>
+        <x:v>Project Orchid existing LI-Conditional; Rush Truck Centers existing conditional LI</x:v>
       </x:c>
       <x:c r="G2" s="39" t="str">
-        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+        <x:v>Legacy conditions water demand impervious area buffer changes parking variance stormwater and traffic circulation still matter</x:v>
       </x:c>
       <x:c r="H2" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Prioritize parcels already zoned industrial and underwrite condition resets as deal costs</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>S01;S30;S31</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="39" t="str">
-        <x:v>Jim Hix</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="B3" s="39" t="str">
-        <x:v>Commissioner District 1</x:v>
+        <x:v>A-2 Agricultural Rural Farm next to an established I-85 US 129 airport or Bill Wright industrial node</x:v>
       </x:c>
       <x:c r="C3" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Urban and/or Industrial FLUM either existing or supportable through map amendment</x:v>
       </x:c>
       <x:c r="D3" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>LI or GI warehouse office-distribution maintenance or industrial park</x:v>
       </x:c>
       <x:c r="E3" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Convertible when it completes an existing industrial pattern and has arterial access utilities buffers and manageable neighbors</x:v>
       </x:c>
       <x:c r="F3" s="39" t="str">
-        <x:v>Member of county legislative body; seconded Wayne Poultry industrial map-amendment approvals in 2022</x:v>
+        <x:v>Tom White EastGroup A-2 to LI; Valentine A-2 to GI; Choice A-2 to GI pending local action; Ingram A-2 to GI</x:v>
       </x:c>
       <x:c r="G3" s="39" t="str">
-        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
+        <x:v>Usually requires road upgrades stream/zoning buffers traffic controls and clear utility path; stronger when industrial use already exists or the site sits in the node</x:v>
       </x:c>
       <x:c r="H3" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Do not buy rural A-2 just because it is cheap; buy A-2 only where the industrial node story is obvious</x:v>
+      </x:c>
+      <x:c r="I3" s="39" t="str">
+        <x:v>S24;S27;S25;S04;S06</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="39" t="str">
-        <x:v>Chas Hardy</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="B4" s="39" t="str">
-        <x:v>Commissioner District 2</x:v>
+        <x:v>Commercial or highway commercial frontage in an industrializing corridor</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Commercial Highway Business or urbanizing corridor with industrial neighbors</x:v>
       </x:c>
       <x:c r="D4" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>LI M-1 or industrial-support commercial support use</x:v>
       </x:c>
       <x:c r="E4" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Good conversion lane where frontage already carries nonresidential intensity and surrounding pattern is industrializing</x:v>
       </x:c>
       <x:c r="F4" s="39" t="str">
-        <x:v>Member of county legislative body</x:v>
+        <x:v>Concord Road C-2 to LI; Taylor &amp; Mathis county A-2 plus city C-2 context to Commerce M-1</x:v>
       </x:c>
       <x:c r="G4" s="39" t="str">
-        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+        <x:v>Traffic access stream buffers parcel assembly annexation and use-specific conditions determine value</x:v>
       </x:c>
       <x:c r="H4" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Commercial frontage can be a strong industrial basis if it is at the right node and not serving a residential plan area</x:v>
+      </x:c>
+      <x:c r="I4" s="39" t="str">
+        <x:v>S32;S35;S36</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="39" t="str">
-        <x:v>Ty Clack</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="B5" s="39" t="str">
-        <x:v>Commissioner District 3</x:v>
+        <x:v>Unincorporated county land at a city edge with utility or access logic</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Urban industrial or commercial context depending on city plan</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>Annexation plus municipal industrial zoning such as Commerce M-1 or Pendergrass/Jefferson industrial district</x:v>
       </x:c>
       <x:c r="E5" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Useful strategic path because city utilities and city zoning may produce cleaner development mechanics than county-only entitlement</x:v>
       </x:c>
       <x:c r="F5" s="39" t="str">
-        <x:v>Member of county legislative body</x:v>
+        <x:v>Taylor &amp; Mathis Commerce annexation rezoning and conditional use</x:v>
       </x:c>
       <x:c r="G5" s="39" t="str">
-        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+        <x:v>Annexation acreage conditions parent-parcel assembly creek exclusions buffers plat conditions and city council approval</x:v>
       </x:c>
       <x:c r="H5" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Model city versus county path before LOI because tax utility impact fee and condition economics can change</x:v>
+      </x:c>
+      <x:c r="I5" s="39" t="str">
+        <x:v>S35;S36</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="39" t="str">
-        <x:v>Marty Seagraves</x:v>
+        <x:v>Orange</x:v>
       </x:c>
       <x:c r="B6" s="39" t="str">
-        <x:v>Commissioner District 4</x:v>
+        <x:v>GI or mixed GI/A-2 land seeking HI or special-use heavy industry</x:v>
       </x:c>
       <x:c r="C6" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Urban/Industrial may help but residential edges still matter</x:v>
       </x:c>
       <x:c r="D6" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>HI special use quarry mining heavy industrial or similar nuisance-potential use</x:v>
       </x:c>
       <x:c r="E6" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Possible but not ordinary warehouse entitlement; customer should expect opposition and heavy conditions</x:v>
       </x:c>
       <x:c r="F6" s="39" t="str">
-        <x:v>Member of county legislative body; official biography emphasizes rural heritage</x:v>
+        <x:v>Jackson Quarry / Vulcan expansion GI and A-2 to HI plus SUP</x:v>
       </x:c>
       <x:c r="G6" s="39" t="str">
-        <x:v>https://jacksoncountygov.com/378/Commissioner-District-4</x:v>
+        <x:v>Split votes road restrictions blasting noise dust screening dark-sky lighting buffers right-of-way donations and truck-routing limits</x:v>
       </x:c>
       <x:c r="H6" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Treat heavy industrial upside as a separate entitlement thesis with legal technical and community budget</x:v>
+      </x:c>
+      <x:c r="I6" s="39" t="str">
+        <x:v>S09;S27</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="39" t="str">
-        <x:v>Cole Elrod</x:v>
+        <x:v>Orange</x:v>
       </x:c>
       <x:c r="B7" s="39" t="str">
-        <x:v>Commissioner District 5</x:v>
+        <x:v>A-2 agricultural land near growth but without a closed local approval</x:v>
       </x:c>
       <x:c r="C7" s="39" t="str">
-        <x:v>Jackson County Board of Commissioners</x:v>
+        <x:v>Industrial or Urban requested but not final</x:v>
       </x:c>
       <x:c r="D7" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>GI LI M-1 or industrial park</x:v>
       </x:c>
       <x:c r="E7" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
+        <x:v>Potentially convertible but not bankable until local action closes; DRI or market status alone is not enough</x:v>
       </x:c>
       <x:c r="F7" s="39" t="str">
-        <x:v>Member of county legislative body</x:v>
+        <x:v>Choice Equipment; Jackson Farms; Project Fortune; Pendergrass Assemblage where industrial relevance is unresolved</x:v>
       </x:c>
       <x:c r="G7" s="39" t="str">
-        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+        <x:v>Local vote annexation utility conditions and parcel baseline control the actual value</x:v>
       </x:c>
       <x:c r="H7" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Use as lead generation and price with entitlement contingency until local ordinance/site-plan proof is in hand</x:v>
+      </x:c>
+      <x:c r="I7" s="39" t="str">
+        <x:v>S08;S25;S26</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="39" t="str">
-        <x:v>Jamie Dove</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="B8" s="39" t="str">
-        <x:v>Planning and Zoning contact / public development leader</x:v>
+        <x:v>Agricultural Forestry Conservation Rural Country Living or Suburban plan context where industrial creates a new edge</x:v>
       </x:c>
       <x:c r="C8" s="39" t="str">
-        <x:v>Jackson County</x:v>
+        <x:v>Agricultural Conservation Suburban Residential or rural-protection designations</x:v>
       </x:c>
       <x:c r="D8" s="39" t="str">
-        <x:v>Unincorporated Jackson County</x:v>
+        <x:v>Urban Industrial HI GI LI or truck-intensive use</x:v>
       </x:c>
       <x:c r="E8" s="39" t="str">
-        <x:v>Staff gatekeeper</x:v>
+        <x:v>Hardest conversion path because the case must change the land-use story before it can win zoning</x:v>
       </x:c>
       <x:c r="F8" s="39" t="str">
-        <x:v>Presented 2022 Wayne Poultry cases and is county planning contact</x:v>
+        <x:v>Whoville Partners withdrawn; East Jackson Quarry adverse compatibility signal; Hwy 124 / Maddox adverse truck/drop-lot signal</x:v>
       </x:c>
       <x:c r="G8" s="39" t="str">
-        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
+        <x:v>Public opposition road/bridge limits environmental constraints residential displacement dust noise water and truck routing dominate</x:v>
       </x:c>
       <x:c r="H8" s="39" t="str">
-        <x:v>High</x:v>
+        <x:v>Do not underwrite as industrial land without a deep entitlement discount and a credible plan-map strategy</x:v>
+      </x:c>
+      <x:c r="I8" s="39" t="str">
+        <x:v>S09;S28;S25</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="39" t="str">
-        <x:v>Steve Wittry</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="B9" s="39" t="str">
-        <x:v>President and CEO</x:v>
+        <x:v>Truck stop diesel fueling drop lot or truck terminal outside a proven truck/industrial node</x:v>
       </x:c>
       <x:c r="C9" s="39" t="str">
-        <x:v>Jackson County Area Chamber / historical Planning Commission participant</x:v>
+        <x:v>Residential or rural plan context or weak local-road network</x:v>
       </x:c>
       <x:c r="D9" s="39" t="str">
-        <x:v>Countywide</x:v>
+        <x:v>HRC truck special use truck drop lot diesel/truck-support use</x:v>
       </x:c>
       <x:c r="E9" s="39" t="str">
-        <x:v>Economic development stakeholder</x:v>
+        <x:v>Truck-support demand is real but the use is not portable across the county; location and circulation decide feasibility</x:v>
       </x:c>
       <x:c r="F9" s="39" t="str">
-        <x:v>Named as Planning Commission chair in the 2022 Wayne Poultry hearing record and leads the Chamber</x:v>
+        <x:v>Hwy 124 / Maddox drop lot adverse signal; 7-Eleven/Peterbilt local action pending; RaceTrac diesel expansion in Jefferson node</x:v>
       </x:c>
       <x:c r="G9" s="39" t="str">
-        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/ArchivedAgenda/_02242022-253?packet=true</x:v>
+        <x:v>Fuel/spill controls driveway geometry truck queues local roads neighboring homes and special-use conditions dominate</x:v>
       </x:c>
       <x:c r="H9" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="39" t="str">
-        <x:v>Stanton Porter</x:v>
-      </x:c>
-      <x:c r="B10" s="39" t="str">
-        <x:v>Zoning counsel</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="str">
-        <x:v>Law Offices of Stell Smith and Mattison</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="str">
-        <x:v>Wayne Poultry Road case</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="str">
-        <x:v>Applicant-side counsel</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="str">
-        <x:v>Represented Hardie Real Estate Group in the 141-acre industrial FLUM amendment cases</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="str">
-        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/ArchivedAgenda/_02242022-253?packet=true</x:v>
-      </x:c>
-      <x:c r="H10" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="39" t="str">
-        <x:v>Hardie Real Estate Group LLC</x:v>
-      </x:c>
-      <x:c r="B11" s="39" t="str">
-        <x:v>Applicant / owner</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="str">
-        <x:v>Hardie Real Estate Group</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="str">
-        <x:v>Wayne Poultry Road case</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="str">
-        <x:v>Applicant-side principal</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="str">
-        <x:v>Applicant for four approved 2022 Industrial FLUM map amendments totaling 141.21 acres</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="str">
-        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
-      </x:c>
-      <x:c r="H11" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="39" t="str">
-        <x:v>Pattillo Industrial Real Estate</x:v>
-      </x:c>
-      <x:c r="B12" s="39" t="str">
-        <x:v>Developer</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="str">
-        <x:v>Pattillo</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="str">
-        <x:v>Project Orchid / McClure Industrial Park</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="str">
-        <x:v>Developer</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="str">
-        <x:v>Filed DRI application for 504000-SF metal manufacturing plant in McClure Industrial Park</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="str">
-        <x:v>http://www.bisnow.com/news/atlanta/industrial/pattillo-aiming-for-metal-manufacturing-plant-in-jackson-county-133702</x:v>
-      </x:c>
-      <x:c r="H12" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="39" t="str">
-        <x:v>Ben Stafford</x:v>
-      </x:c>
-      <x:c r="B13" s="39" t="str">
-        <x:v>Vice President</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="str">
-        <x:v>Pattillo Industrial Real Estate</x:v>
-      </x:c>
-      <x:c r="D13" s="39" t="str">
-        <x:v>Project Orchid / McClure Industrial Park</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="str">
-        <x:v>Developer representative</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="str">
-        <x:v>Quoted by press as Pattillo VP in connection with Project Orchid</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="str">
-        <x:v>http://www.bisnow.com/news/atlanta/industrial/pattillo-aiming-for-metal-manufacturing-plant-in-jackson-county-133702</x:v>
-      </x:c>
-      <x:c r="H13" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="39" t="str">
-        <x:v>Brian Brumfield</x:v>
-      </x:c>
-      <x:c r="B14" s="39" t="str">
-        <x:v>Applicant representative</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="str">
-        <x:v>Eberly and Associates</x:v>
-      </x:c>
-      <x:c r="D14" s="39" t="str">
-        <x:v>Rush Truck Centers condition modification</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="str">
-        <x:v>Applicant-side consultant</x:v>
-      </x:c>
-      <x:c r="F14" s="39" t="str">
-        <x:v>Named as applicant representative for the truck-service LI condition modification</x:v>
-      </x:c>
-      <x:c r="G14" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
-      </x:c>
-      <x:c r="H14" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="39" t="str">
-        <x:v>Rush Truck Centers of Georgia Inc.</x:v>
-      </x:c>
-      <x:c r="B15" s="39" t="str">
-        <x:v>Applicant</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="str">
-        <x:v>Rush Truck Centers</x:v>
-      </x:c>
-      <x:c r="D15" s="39" t="str">
-        <x:v>Jefferson I-85 / Hog Mountain Road</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="str">
-        <x:v>End user / applicant</x:v>
-      </x:c>
-      <x:c r="F15" s="39" t="str">
-        <x:v>Applicant for conditional LI modification and truck-service use</x:v>
-      </x:c>
-      <x:c r="G15" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
-      </x:c>
-      <x:c r="H15" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="39" t="str">
-        <x:v>JM Business Park IV LLC</x:v>
-      </x:c>
-      <x:c r="B16" s="39" t="str">
-        <x:v>Property owner</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="str">
-        <x:v>JM Business Park IV LLC</x:v>
-      </x:c>
-      <x:c r="D16" s="39" t="str">
-        <x:v>Jefferson I-85 / Hog Mountain Road</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="str">
-        <x:v>Landowner</x:v>
-      </x:c>
-      <x:c r="F16" s="39" t="str">
-        <x:v>Named property owner for Rush Truck Centers application</x:v>
-      </x:c>
-      <x:c r="G16" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
-      </x:c>
-      <x:c r="H16" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="39" t="str">
-        <x:v>RaceTrac Inc.</x:v>
-      </x:c>
-      <x:c r="B17" s="39" t="str">
-        <x:v>Developer / operator</x:v>
-      </x:c>
-      <x:c r="C17" s="39" t="str">
-        <x:v>RaceTrac</x:v>
-      </x:c>
-      <x:c r="D17" s="39" t="str">
-        <x:v>Jefferson I-85 node</x:v>
-      </x:c>
-      <x:c r="E17" s="39" t="str">
-        <x:v>End user / applicant</x:v>
-      </x:c>
-      <x:c r="F17" s="39" t="str">
-        <x:v>Applicant proposing travel-center diesel expansion near I-85</x:v>
-      </x:c>
-      <x:c r="G17" s="39" t="str">
-        <x:v>https://negrc.org/uploads/sites/4/2025/04/DRI4420.RacetracExtendedDieselOffer.Jefferson.FinalReport.pdf</x:v>
-      </x:c>
-      <x:c r="H17" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="39" t="str">
-        <x:v>Dawn Maddox</x:v>
-      </x:c>
-      <x:c r="B18" s="39" t="str">
-        <x:v>Mayor</x:v>
-      </x:c>
-      <x:c r="C18" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D18" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E18" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F18" s="39" t="str">
-        <x:v>Mayor in Jefferson council-manager government</x:v>
-      </x:c>
-      <x:c r="G18" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H18" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="39" t="str">
-        <x:v>Steve Kinney</x:v>
-      </x:c>
-      <x:c r="B19" s="39" t="str">
-        <x:v>Mayor Pro Tempore / District 1 Councilmember</x:v>
-      </x:c>
-      <x:c r="C19" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D19" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E19" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F19" s="39" t="str">
-        <x:v>City Council member</x:v>
-      </x:c>
-      <x:c r="G19" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H19" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="39" t="str">
-        <x:v>Annette Studivant</x:v>
-      </x:c>
-      <x:c r="B20" s="39" t="str">
-        <x:v>District 2 Councilmember</x:v>
-      </x:c>
-      <x:c r="C20" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D20" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E20" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F20" s="39" t="str">
-        <x:v>City Council member</x:v>
-      </x:c>
-      <x:c r="G20" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H20" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="39" t="str">
-        <x:v>Cody Cain</x:v>
-      </x:c>
-      <x:c r="B21" s="39" t="str">
-        <x:v>District 3 Councilmember</x:v>
-      </x:c>
-      <x:c r="C21" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D21" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E21" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F21" s="39" t="str">
-        <x:v>City Council member</x:v>
-      </x:c>
-      <x:c r="G21" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H21" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="39" t="str">
-        <x:v>Mark Mobley</x:v>
-      </x:c>
-      <x:c r="B22" s="39" t="str">
-        <x:v>District 4 Councilmember</x:v>
-      </x:c>
-      <x:c r="C22" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D22" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E22" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F22" s="39" t="str">
-        <x:v>City Council member</x:v>
-      </x:c>
-      <x:c r="G22" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H22" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="39" t="str">
-        <x:v>Alex Crawford</x:v>
-      </x:c>
-      <x:c r="B23" s="39" t="str">
-        <x:v>District 5 Councilmember</x:v>
-      </x:c>
-      <x:c r="C23" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D23" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E23" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F23" s="39" t="str">
-        <x:v>City Council member</x:v>
-      </x:c>
-      <x:c r="G23" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
-      </x:c>
-      <x:c r="H23" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="39" t="str">
-        <x:v>Rob Alexander</x:v>
-      </x:c>
-      <x:c r="B24" s="39" t="str">
-        <x:v>City Attorney</x:v>
-      </x:c>
-      <x:c r="C24" s="39" t="str">
-        <x:v>Davidson Hopkins and Alexander</x:v>
-      </x:c>
-      <x:c r="D24" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E24" s="39" t="str">
-        <x:v>Public counsel</x:v>
-      </x:c>
-      <x:c r="F24" s="39" t="str">
-        <x:v>Listed official City Attorney</x:v>
-      </x:c>
-      <x:c r="G24" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/m/directory</x:v>
-      </x:c>
-      <x:c r="H24" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="39" t="str">
-        <x:v>Priscilla Murphy</x:v>
-      </x:c>
-      <x:c r="B25" s="39" t="str">
-        <x:v>City Manager</x:v>
-      </x:c>
-      <x:c r="C25" s="39" t="str">
-        <x:v>City of Jefferson</x:v>
-      </x:c>
-      <x:c r="D25" s="39" t="str">
-        <x:v>Jefferson</x:v>
-      </x:c>
-      <x:c r="E25" s="39" t="str">
-        <x:v>Senior staff</x:v>
-      </x:c>
-      <x:c r="F25" s="39" t="str">
-        <x:v>Listed official City Manager</x:v>
-      </x:c>
-      <x:c r="G25" s="39" t="str">
-        <x:v>https://www.jeffersonga.gov/m/directory</x:v>
-      </x:c>
-      <x:c r="H25" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="39" t="str">
-        <x:v>Trammell Crow Company</x:v>
-      </x:c>
-      <x:c r="B26" s="39" t="str">
-        <x:v>Developer</x:v>
-      </x:c>
-      <x:c r="C26" s="39" t="str">
-        <x:v>Trammell Crow Company</x:v>
-      </x:c>
-      <x:c r="D26" s="39" t="str">
-        <x:v>Jackson 85 North</x:v>
-      </x:c>
-      <x:c r="E26" s="39" t="str">
-        <x:v>Developer</x:v>
-      </x:c>
-      <x:c r="F26" s="39" t="str">
-        <x:v>Developer of completed Pendergrass Class-A warehouse park</x:v>
-      </x:c>
-      <x:c r="G26" s="39" t="str">
-        <x:v>http://www.trammellcrow.com/projects/jackson-85-north</x:v>
-      </x:c>
-      <x:c r="H26" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="39" t="str">
-        <x:v>CBRE Investment Management</x:v>
-      </x:c>
-      <x:c r="B27" s="39" t="str">
-        <x:v>Capital partner</x:v>
-      </x:c>
-      <x:c r="C27" s="39" t="str">
-        <x:v>CBRE Investment Management</x:v>
-      </x:c>
-      <x:c r="D27" s="39" t="str">
-        <x:v>Jackson 85 North</x:v>
-      </x:c>
-      <x:c r="E27" s="39" t="str">
-        <x:v>Capital partner</x:v>
-      </x:c>
-      <x:c r="F27" s="39" t="str">
-        <x:v>Joint venture partner reported for Jackson 85 North phase one</x:v>
-      </x:c>
-      <x:c r="G27" s="39" t="str">
-        <x:v>https://rebusinessonline.com/category/georgia/page/29/</x:v>
-      </x:c>
-      <x:c r="H27" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="39" t="str">
-        <x:v>Evans</x:v>
-      </x:c>
-      <x:c r="B28" s="39" t="str">
-        <x:v>General contractor</x:v>
-      </x:c>
-      <x:c r="C28" s="39" t="str">
-        <x:v>Evans General Contractors</x:v>
-      </x:c>
-      <x:c r="D28" s="39" t="str">
-        <x:v>Jackson 85 North phase two</x:v>
-      </x:c>
-      <x:c r="E28" s="39" t="str">
-        <x:v>General contractor</x:v>
-      </x:c>
-      <x:c r="F28" s="39" t="str">
-        <x:v>Reported design-build general contractor for phase two</x:v>
-      </x:c>
-      <x:c r="G28" s="39" t="str">
-        <x:v>https://rebusinessonline.com/category/georgia/page/29/</x:v>
-      </x:c>
-      <x:c r="H28" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="39" t="str">
-        <x:v>Stephanie Harris</x:v>
-      </x:c>
-      <x:c r="B29" s="39" t="str">
-        <x:v>Senior Development Manager</x:v>
-      </x:c>
-      <x:c r="C29" s="39" t="str">
-        <x:v>Trammell Crow Company</x:v>
-      </x:c>
-      <x:c r="D29" s="39" t="str">
-        <x:v>Jackson 85 North</x:v>
-      </x:c>
-      <x:c r="E29" s="39" t="str">
-        <x:v>Developer representative</x:v>
-      </x:c>
-      <x:c r="F29" s="39" t="str">
-        <x:v>Listed project contact</x:v>
-      </x:c>
-      <x:c r="G29" s="39" t="str">
-        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
-      </x:c>
-      <x:c r="H29" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="39" t="str">
-        <x:v>Drew Fredrick</x:v>
-      </x:c>
-      <x:c r="B30" s="39" t="str">
-        <x:v>Executive Vice President</x:v>
-      </x:c>
-      <x:c r="C30" s="39" t="str">
-        <x:v>Trammell Crow Company</x:v>
-      </x:c>
-      <x:c r="D30" s="39" t="str">
-        <x:v>Jackson 85 North</x:v>
-      </x:c>
-      <x:c r="E30" s="39" t="str">
-        <x:v>Developer representative</x:v>
-      </x:c>
-      <x:c r="F30" s="39" t="str">
-        <x:v>Listed project contact</x:v>
-      </x:c>
-      <x:c r="G30" s="39" t="str">
-        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
-      </x:c>
-      <x:c r="H30" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="39" t="str">
-        <x:v>Tyler Cooksey</x:v>
-      </x:c>
-      <x:c r="B31" s="39" t="str">
-        <x:v>Senior Vice President</x:v>
-      </x:c>
-      <x:c r="C31" s="39" t="str">
-        <x:v>Trammell Crow Company</x:v>
-      </x:c>
-      <x:c r="D31" s="39" t="str">
-        <x:v>Jackson 85 North</x:v>
-      </x:c>
-      <x:c r="E31" s="39" t="str">
-        <x:v>Developer representative</x:v>
-      </x:c>
-      <x:c r="F31" s="39" t="str">
-        <x:v>Listed project contact</x:v>
-      </x:c>
-      <x:c r="G31" s="39" t="str">
-        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
-      </x:c>
-      <x:c r="H31" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="39" t="str">
-        <x:v>Bill Ellis</x:v>
-      </x:c>
-      <x:c r="B32" s="39" t="str">
-        <x:v>Mayor</x:v>
-      </x:c>
-      <x:c r="C32" s="39" t="str">
-        <x:v>City of Pendergrass</x:v>
-      </x:c>
-      <x:c r="D32" s="39" t="str">
-        <x:v>Pendergrass</x:v>
-      </x:c>
-      <x:c r="E32" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F32" s="39" t="str">
-        <x:v>Mayor in strong-mayor government</x:v>
-      </x:c>
-      <x:c r="G32" s="39" t="str">
-        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
-      </x:c>
-      <x:c r="H32" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="39" t="str">
-        <x:v>Gabriel Gomez</x:v>
-      </x:c>
-      <x:c r="B33" s="39" t="str">
-        <x:v>Mayor Pro Tem / Councilmember</x:v>
-      </x:c>
-      <x:c r="C33" s="39" t="str">
-        <x:v>City of Pendergrass</x:v>
-      </x:c>
-      <x:c r="D33" s="39" t="str">
-        <x:v>Pendergrass</x:v>
-      </x:c>
-      <x:c r="E33" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F33" s="39" t="str">
-        <x:v>Current councilmember and Mayor Pro Tem</x:v>
-      </x:c>
-      <x:c r="G33" s="39" t="str">
-        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
-      </x:c>
-      <x:c r="H33" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="39" t="str">
-        <x:v>Laura Bigley</x:v>
-      </x:c>
-      <x:c r="B34" s="39" t="str">
-        <x:v>Councilmember</x:v>
-      </x:c>
-      <x:c r="C34" s="39" t="str">
-        <x:v>City of Pendergrass</x:v>
-      </x:c>
-      <x:c r="D34" s="39" t="str">
-        <x:v>Pendergrass</x:v>
-      </x:c>
-      <x:c r="E34" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F34" s="39" t="str">
-        <x:v>Current councilmember</x:v>
-      </x:c>
-      <x:c r="G34" s="39" t="str">
-        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
-      </x:c>
-      <x:c r="H34" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="39" t="str">
-        <x:v>Bob Carter</x:v>
-      </x:c>
-      <x:c r="B35" s="39" t="str">
-        <x:v>Councilmember</x:v>
-      </x:c>
-      <x:c r="C35" s="39" t="str">
-        <x:v>City of Pendergrass</x:v>
-      </x:c>
-      <x:c r="D35" s="39" t="str">
-        <x:v>Pendergrass</x:v>
-      </x:c>
-      <x:c r="E35" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F35" s="39" t="str">
-        <x:v>Current councilmember</x:v>
-      </x:c>
-      <x:c r="G35" s="39" t="str">
-        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
-      </x:c>
-      <x:c r="H35" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="39" t="str">
-        <x:v>Sylvia Basak</x:v>
-      </x:c>
-      <x:c r="B36" s="39" t="str">
-        <x:v>Councilmember</x:v>
-      </x:c>
-      <x:c r="C36" s="39" t="str">
-        <x:v>City of Pendergrass</x:v>
-      </x:c>
-      <x:c r="D36" s="39" t="str">
-        <x:v>Pendergrass</x:v>
-      </x:c>
-      <x:c r="E36" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F36" s="39" t="str">
-        <x:v>Current councilmember</x:v>
-      </x:c>
-      <x:c r="G36" s="39" t="str">
-        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
-      </x:c>
-      <x:c r="H36" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="39" t="str">
-        <x:v>Dr. J. Clark Hill III</x:v>
-      </x:c>
-      <x:c r="B37" s="39" t="str">
-        <x:v>Mayor</x:v>
-      </x:c>
-      <x:c r="C37" s="39" t="str">
-        <x:v>City of Commerce</x:v>
-      </x:c>
-      <x:c r="D37" s="39" t="str">
-        <x:v>Commerce</x:v>
-      </x:c>
-      <x:c r="E37" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F37" s="39" t="str">
-        <x:v>Mayor and chief executive officer</x:v>
-      </x:c>
-      <x:c r="G37" s="39" t="str">
-        <x:v>https://www.commercega.gov/government/elected-officials</x:v>
-      </x:c>
-      <x:c r="H37" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="39" t="str">
-        <x:v>Keith Burchett</x:v>
-      </x:c>
-      <x:c r="B38" s="39" t="str">
-        <x:v>Mayor Pro Tem</x:v>
-      </x:c>
-      <x:c r="C38" s="39" t="str">
-        <x:v>City of Commerce</x:v>
-      </x:c>
-      <x:c r="D38" s="39" t="str">
-        <x:v>Commerce</x:v>
-      </x:c>
-      <x:c r="E38" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F38" s="39" t="str">
-        <x:v>Mayor Pro Tem</x:v>
-      </x:c>
-      <x:c r="G38" s="39" t="str">
-        <x:v>https://www.commercega.gov/government/elected-officials</x:v>
-      </x:c>
-      <x:c r="H38" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="39" t="str">
-        <x:v>Matthew Hailey</x:v>
-      </x:c>
-      <x:c r="B39" s="39" t="str">
-        <x:v>City Manager</x:v>
-      </x:c>
-      <x:c r="C39" s="39" t="str">
-        <x:v>City of Commerce</x:v>
-      </x:c>
-      <x:c r="D39" s="39" t="str">
-        <x:v>Commerce</x:v>
-      </x:c>
-      <x:c r="E39" s="39" t="str">
-        <x:v>Senior staff</x:v>
-      </x:c>
-      <x:c r="F39" s="39" t="str">
-        <x:v>Listed official City Manager</x:v>
-      </x:c>
-      <x:c r="G39" s="39" t="str">
-        <x:v>https://commercega.gov/government</x:v>
-      </x:c>
-      <x:c r="H39" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="39" t="str">
-        <x:v>Leland Smith</x:v>
-      </x:c>
-      <x:c r="B40" s="39" t="str">
-        <x:v>Planning and Zoning Administrator</x:v>
-      </x:c>
-      <x:c r="C40" s="39" t="str">
-        <x:v>City of Commerce</x:v>
-      </x:c>
-      <x:c r="D40" s="39" t="str">
-        <x:v>Taylor &amp; Mathis Commerce case</x:v>
-      </x:c>
-      <x:c r="E40" s="39" t="str">
-        <x:v>Staff gatekeeper</x:v>
-      </x:c>
-      <x:c r="F40" s="39" t="str">
-        <x:v>Presented annexation rezoning and conditional use to Planning Commission and City Council</x:v>
-      </x:c>
-      <x:c r="G40" s="39" t="str">
-        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
-      </x:c>
-      <x:c r="H40" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="39" t="str">
-        <x:v>Dillon Anthony</x:v>
-      </x:c>
-      <x:c r="B41" s="39" t="str">
-        <x:v>Planning and Development Superintendent / Building Inspector</x:v>
-      </x:c>
-      <x:c r="C41" s="39" t="str">
-        <x:v>City of Commerce</x:v>
-      </x:c>
-      <x:c r="D41" s="39" t="str">
-        <x:v>Taylor &amp; Mathis Commerce case</x:v>
-      </x:c>
-      <x:c r="E41" s="39" t="str">
-        <x:v>Staff gatekeeper</x:v>
-      </x:c>
-      <x:c r="F41" s="39" t="str">
-        <x:v>Requested/presented Taylor &amp; Mathis agenda items and clarified acreage/parcel details</x:v>
-      </x:c>
-      <x:c r="G41" s="39" t="str">
-        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
-      </x:c>
-      <x:c r="H41" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="39" t="str">
-        <x:v>Taylor &amp; Mathis Inc.</x:v>
-      </x:c>
-      <x:c r="B42" s="39" t="str">
-        <x:v>Applicant</x:v>
-      </x:c>
-      <x:c r="C42" s="39" t="str">
-        <x:v>Taylor &amp; Mathis Inc.</x:v>
-      </x:c>
-      <x:c r="D42" s="39" t="str">
-        <x:v>Commerce distribution center / truck terminal</x:v>
-      </x:c>
-      <x:c r="E42" s="39" t="str">
-        <x:v>Developer/applicant</x:v>
-      </x:c>
-      <x:c r="F42" s="39" t="str">
-        <x:v>Applicant for annexation rezoning and conditional use for 121.373-acre distribution center with truck terminals and warehouse/storage</x:v>
-      </x:c>
-      <x:c r="G42" s="39" t="str">
-        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
-      </x:c>
-      <x:c r="H42" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="39" t="str">
-        <x:v>Mahaffey Pickens Tucker LLP</x:v>
-      </x:c>
-      <x:c r="B43" s="39" t="str">
-        <x:v>Zoning counsel/applicant representative</x:v>
-      </x:c>
-      <x:c r="C43" s="39" t="str">
-        <x:v>Mahaffey Pickens Tucker LLP</x:v>
-      </x:c>
-      <x:c r="D43" s="39" t="str">
-        <x:v>Commerce distribution center / truck terminal</x:v>
-      </x:c>
-      <x:c r="E43" s="39" t="str">
-        <x:v>Zoning counsel</x:v>
-      </x:c>
-      <x:c r="F43" s="39" t="str">
-        <x:v>Listed as c/o applicant representative for Taylor &amp; Mathis Commerce cases</x:v>
-      </x:c>
-      <x:c r="G43" s="39" t="str">
-        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
-      </x:c>
-      <x:c r="H43" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="39" t="str">
-        <x:v>Anthony L. Wood Jr. and Benjamin A. Wood</x:v>
-      </x:c>
-      <x:c r="B44" s="39" t="str">
-        <x:v>Property owners</x:v>
-      </x:c>
-      <x:c r="C44" s="39" t="str">
-        <x:v>Private owners</x:v>
-      </x:c>
-      <x:c r="D44" s="39" t="str">
-        <x:v>Commerce distribution center / truck terminal</x:v>
-      </x:c>
-      <x:c r="E44" s="39" t="str">
-        <x:v>Landowner</x:v>
-      </x:c>
-      <x:c r="F44" s="39" t="str">
-        <x:v>Listed as property owners for parcels 020 002 and 020 008</x:v>
-      </x:c>
-      <x:c r="G44" s="39" t="str">
-        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
-      </x:c>
-      <x:c r="H44" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="39" t="str">
-        <x:v>Debbie Martin</x:v>
-      </x:c>
-      <x:c r="B45" s="39" t="str">
-        <x:v>Mayor</x:v>
-      </x:c>
-      <x:c r="C45" s="39" t="str">
-        <x:v>City of Hoschton</x:v>
-      </x:c>
-      <x:c r="D45" s="39" t="str">
-        <x:v>Hoschton</x:v>
-      </x:c>
-      <x:c r="E45" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F45" s="39" t="str">
-        <x:v>Current Mayor</x:v>
-      </x:c>
-      <x:c r="G45" s="39" t="str">
-        <x:v>https://www.cityofhoschton.net/directory-listing/mariya-bentz</x:v>
-      </x:c>
-      <x:c r="H45" s="39" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="39" t="str">
-        <x:v>Kurt Ward</x:v>
-      </x:c>
-      <x:c r="B46" s="39" t="str">
-        <x:v>Mayor</x:v>
-      </x:c>
-      <x:c r="C46" s="39" t="str">
-        <x:v>Town of Braselton</x:v>
-      </x:c>
-      <x:c r="D46" s="39" t="str">
-        <x:v>Braselton Jackson County area</x:v>
-      </x:c>
-      <x:c r="E46" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F46" s="39" t="str">
-        <x:v>Mayor and voting member of Town Council</x:v>
-      </x:c>
-      <x:c r="G46" s="39" t="str">
-        <x:v>https://www.braseltonmayor.org/town-council</x:v>
-      </x:c>
-      <x:c r="H46" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="39" t="str">
-        <x:v>Becky Richardson</x:v>
-      </x:c>
-      <x:c r="B47" s="39" t="str">
-        <x:v>District 1 Councilmember / Mayor Pro Tem</x:v>
-      </x:c>
-      <x:c r="C47" s="39" t="str">
-        <x:v>Town of Braselton</x:v>
-      </x:c>
-      <x:c r="D47" s="39" t="str">
-        <x:v>Braselton Jackson County area</x:v>
-      </x:c>
-      <x:c r="E47" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F47" s="39" t="str">
-        <x:v>Listed Town Council member</x:v>
-      </x:c>
-      <x:c r="G47" s="39" t="str">
-        <x:v>https://www.braseltonmayor.org/town-council</x:v>
-      </x:c>
-      <x:c r="H47" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="39" t="str">
-        <x:v>Richard Harper</x:v>
-      </x:c>
-      <x:c r="B48" s="39" t="str">
-        <x:v>District 2 Councilmember</x:v>
-      </x:c>
-      <x:c r="C48" s="39" t="str">
-        <x:v>Town of Braselton</x:v>
-      </x:c>
-      <x:c r="D48" s="39" t="str">
-        <x:v>Braselton Jackson County area</x:v>
-      </x:c>
-      <x:c r="E48" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F48" s="39" t="str">
-        <x:v>Listed Town Council member</x:v>
-      </x:c>
-      <x:c r="G48" s="39" t="str">
-        <x:v>https://www.braseltonmayor.org/town-council</x:v>
-      </x:c>
-      <x:c r="H48" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="39" t="str">
-        <x:v>Tom Logan</x:v>
-      </x:c>
-      <x:c r="B49" s="39" t="str">
-        <x:v>District 3 Councilmember</x:v>
-      </x:c>
-      <x:c r="C49" s="39" t="str">
-        <x:v>Town of Braselton</x:v>
-      </x:c>
-      <x:c r="D49" s="39" t="str">
-        <x:v>Braselton Jackson County area</x:v>
-      </x:c>
-      <x:c r="E49" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F49" s="39" t="str">
-        <x:v>Listed Town Council member</x:v>
-      </x:c>
-      <x:c r="G49" s="39" t="str">
-        <x:v>https://www.braseltonmayor.org/town-council</x:v>
-      </x:c>
-      <x:c r="H49" s="39" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="39" t="str">
-        <x:v>James Murphy</x:v>
-      </x:c>
-      <x:c r="B50" s="39" t="str">
-        <x:v>District 4 Councilmember</x:v>
-      </x:c>
-      <x:c r="C50" s="39" t="str">
-        <x:v>Town of Braselton</x:v>
-      </x:c>
-      <x:c r="D50" s="39" t="str">
-        <x:v>Braselton Jackson County area</x:v>
-      </x:c>
-      <x:c r="E50" s="39" t="str">
-        <x:v>Current decision-maker</x:v>
-      </x:c>
-      <x:c r="F50" s="39" t="str">
-        <x:v>Listed Town Council member</x:v>
-      </x:c>
-      <x:c r="G50" s="39" t="str">
-        <x:v>https://www.braseltonmayor.org/town-council</x:v>
-      </x:c>
-      <x:c r="H50" s="39" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Only pursue truck-support sites where interchange access and surrounding industrial/commercial pattern are already obvious</x:v>
+      </x:c>
+      <x:c r="I9" s="39" t="str">
+        <x:v>S07;S25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3768,6 +2731,1325 @@
     <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="B1" s="44" t="str">
+        <x:v>role</x:v>
+      </x:c>
+      <x:c r="C1" s="44" t="str">
+        <x:v>organization</x:v>
+      </x:c>
+      <x:c r="D1" s="44" t="str">
+        <x:v>jurisdiction_or_case</x:v>
+      </x:c>
+      <x:c r="E1" s="44" t="str">
+        <x:v>player_type</x:v>
+      </x:c>
+      <x:c r="F1" s="44" t="str">
+        <x:v>evidence_based_signal</x:v>
+      </x:c>
+      <x:c r="G1" s="44" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="H1" s="44" t="str">
+        <x:v>confidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="39" t="str">
+        <x:v>Marty Clark</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>Chairman</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>At-large chair of the legislative body for county zoning; former Planning Commission chair</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="39" t="str">
+        <x:v>Jim Hix</x:v>
+      </x:c>
+      <x:c r="B3" s="39" t="str">
+        <x:v>Commissioner District 1</x:v>
+      </x:c>
+      <x:c r="C3" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D3" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E3" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F3" s="39" t="str">
+        <x:v>Member of county legislative body; seconded Wayne Poultry industrial map-amendment approvals in 2022</x:v>
+      </x:c>
+      <x:c r="G3" s="39" t="str">
+        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
+      </x:c>
+      <x:c r="H3" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="39" t="str">
+        <x:v>Chas Hardy</x:v>
+      </x:c>
+      <x:c r="B4" s="39" t="str">
+        <x:v>Commissioner District 2</x:v>
+      </x:c>
+      <x:c r="C4" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D4" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E4" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F4" s="39" t="str">
+        <x:v>Member of county legislative body</x:v>
+      </x:c>
+      <x:c r="G4" s="39" t="str">
+        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+      </x:c>
+      <x:c r="H4" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="39" t="str">
+        <x:v>Ty Clack</x:v>
+      </x:c>
+      <x:c r="B5" s="39" t="str">
+        <x:v>Commissioner District 3</x:v>
+      </x:c>
+      <x:c r="C5" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D5" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E5" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F5" s="39" t="str">
+        <x:v>Member of county legislative body</x:v>
+      </x:c>
+      <x:c r="G5" s="39" t="str">
+        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+      </x:c>
+      <x:c r="H5" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="39" t="str">
+        <x:v>Marty Seagraves</x:v>
+      </x:c>
+      <x:c r="B6" s="39" t="str">
+        <x:v>Commissioner District 4</x:v>
+      </x:c>
+      <x:c r="C6" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D6" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E6" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F6" s="39" t="str">
+        <x:v>Member of county legislative body; official biography emphasizes rural heritage</x:v>
+      </x:c>
+      <x:c r="G6" s="39" t="str">
+        <x:v>https://jacksoncountygov.com/378/Commissioner-District-4</x:v>
+      </x:c>
+      <x:c r="H6" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="39" t="str">
+        <x:v>Cole Elrod</x:v>
+      </x:c>
+      <x:c r="B7" s="39" t="str">
+        <x:v>Commissioner District 5</x:v>
+      </x:c>
+      <x:c r="C7" s="39" t="str">
+        <x:v>Jackson County Board of Commissioners</x:v>
+      </x:c>
+      <x:c r="D7" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E7" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F7" s="39" t="str">
+        <x:v>Member of county legislative body</x:v>
+      </x:c>
+      <x:c r="G7" s="39" t="str">
+        <x:v>https://jacksoncountygov.com/373/Board-of-Commissioners</x:v>
+      </x:c>
+      <x:c r="H7" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="39" t="str">
+        <x:v>Jamie Dove</x:v>
+      </x:c>
+      <x:c r="B8" s="39" t="str">
+        <x:v>Planning and Zoning contact / public development leader</x:v>
+      </x:c>
+      <x:c r="C8" s="39" t="str">
+        <x:v>Jackson County</x:v>
+      </x:c>
+      <x:c r="D8" s="39" t="str">
+        <x:v>Unincorporated Jackson County</x:v>
+      </x:c>
+      <x:c r="E8" s="39" t="str">
+        <x:v>Staff gatekeeper</x:v>
+      </x:c>
+      <x:c r="F8" s="39" t="str">
+        <x:v>Presented 2022 Wayne Poultry cases and is county planning contact</x:v>
+      </x:c>
+      <x:c r="G8" s="39" t="str">
+        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
+      </x:c>
+      <x:c r="H8" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="39" t="str">
+        <x:v>Steve Wittry</x:v>
+      </x:c>
+      <x:c r="B9" s="39" t="str">
+        <x:v>President and CEO</x:v>
+      </x:c>
+      <x:c r="C9" s="39" t="str">
+        <x:v>Jackson County Area Chamber / historical Planning Commission participant</x:v>
+      </x:c>
+      <x:c r="D9" s="39" t="str">
+        <x:v>Countywide</x:v>
+      </x:c>
+      <x:c r="E9" s="39" t="str">
+        <x:v>Economic development stakeholder</x:v>
+      </x:c>
+      <x:c r="F9" s="39" t="str">
+        <x:v>Named as Planning Commission chair in the 2022 Wayne Poultry hearing record and leads the Chamber</x:v>
+      </x:c>
+      <x:c r="G9" s="39" t="str">
+        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/ArchivedAgenda/_02242022-253?packet=true</x:v>
+      </x:c>
+      <x:c r="H9" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="39" t="str">
+        <x:v>Stanton Porter</x:v>
+      </x:c>
+      <x:c r="B10" s="39" t="str">
+        <x:v>Zoning counsel</x:v>
+      </x:c>
+      <x:c r="C10" s="39" t="str">
+        <x:v>Law Offices of Stell Smith and Mattison</x:v>
+      </x:c>
+      <x:c r="D10" s="39" t="str">
+        <x:v>Wayne Poultry Road case</x:v>
+      </x:c>
+      <x:c r="E10" s="39" t="str">
+        <x:v>Applicant-side counsel</x:v>
+      </x:c>
+      <x:c r="F10" s="39" t="str">
+        <x:v>Represented Hardie Real Estate Group in the 141-acre industrial FLUM amendment cases</x:v>
+      </x:c>
+      <x:c r="G10" s="39" t="str">
+        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/ArchivedAgenda/_02242022-253?packet=true</x:v>
+      </x:c>
+      <x:c r="H10" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="39" t="str">
+        <x:v>Hardie Real Estate Group LLC</x:v>
+      </x:c>
+      <x:c r="B11" s="39" t="str">
+        <x:v>Applicant / owner</x:v>
+      </x:c>
+      <x:c r="C11" s="39" t="str">
+        <x:v>Hardie Real Estate Group</x:v>
+      </x:c>
+      <x:c r="D11" s="39" t="str">
+        <x:v>Wayne Poultry Road case</x:v>
+      </x:c>
+      <x:c r="E11" s="39" t="str">
+        <x:v>Applicant-side principal</x:v>
+      </x:c>
+      <x:c r="F11" s="39" t="str">
+        <x:v>Applicant for four approved 2022 Industrial FLUM map amendments totaling 141.21 acres</x:v>
+      </x:c>
+      <x:c r="G11" s="39" t="str">
+        <x:v>https://www.jacksoncountygov.com/AgendaCenter/ViewFile/Minutes/_02212022-465</x:v>
+      </x:c>
+      <x:c r="H11" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="39" t="str">
+        <x:v>Pattillo Industrial Real Estate</x:v>
+      </x:c>
+      <x:c r="B12" s="39" t="str">
+        <x:v>Developer</x:v>
+      </x:c>
+      <x:c r="C12" s="39" t="str">
+        <x:v>Pattillo</x:v>
+      </x:c>
+      <x:c r="D12" s="39" t="str">
+        <x:v>Project Orchid / McClure Industrial Park</x:v>
+      </x:c>
+      <x:c r="E12" s="39" t="str">
+        <x:v>Developer</x:v>
+      </x:c>
+      <x:c r="F12" s="39" t="str">
+        <x:v>Filed DRI application for 504000-SF metal manufacturing plant in McClure Industrial Park</x:v>
+      </x:c>
+      <x:c r="G12" s="39" t="str">
+        <x:v>http://www.bisnow.com/news/atlanta/industrial/pattillo-aiming-for-metal-manufacturing-plant-in-jackson-county-133702</x:v>
+      </x:c>
+      <x:c r="H12" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="39" t="str">
+        <x:v>Ben Stafford</x:v>
+      </x:c>
+      <x:c r="B13" s="39" t="str">
+        <x:v>Vice President</x:v>
+      </x:c>
+      <x:c r="C13" s="39" t="str">
+        <x:v>Pattillo Industrial Real Estate</x:v>
+      </x:c>
+      <x:c r="D13" s="39" t="str">
+        <x:v>Project Orchid / McClure Industrial Park</x:v>
+      </x:c>
+      <x:c r="E13" s="39" t="str">
+        <x:v>Developer representative</x:v>
+      </x:c>
+      <x:c r="F13" s="39" t="str">
+        <x:v>Quoted by press as Pattillo VP in connection with Project Orchid</x:v>
+      </x:c>
+      <x:c r="G13" s="39" t="str">
+        <x:v>http://www.bisnow.com/news/atlanta/industrial/pattillo-aiming-for-metal-manufacturing-plant-in-jackson-county-133702</x:v>
+      </x:c>
+      <x:c r="H13" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="39" t="str">
+        <x:v>Brian Brumfield</x:v>
+      </x:c>
+      <x:c r="B14" s="39" t="str">
+        <x:v>Applicant representative</x:v>
+      </x:c>
+      <x:c r="C14" s="39" t="str">
+        <x:v>Eberly and Associates</x:v>
+      </x:c>
+      <x:c r="D14" s="39" t="str">
+        <x:v>Rush Truck Centers condition modification</x:v>
+      </x:c>
+      <x:c r="E14" s="39" t="str">
+        <x:v>Applicant-side consultant</x:v>
+      </x:c>
+      <x:c r="F14" s="39" t="str">
+        <x:v>Named as applicant representative for the truck-service LI condition modification</x:v>
+      </x:c>
+      <x:c r="G14" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
+      </x:c>
+      <x:c r="H14" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="39" t="str">
+        <x:v>Rush Truck Centers of Georgia Inc.</x:v>
+      </x:c>
+      <x:c r="B15" s="39" t="str">
+        <x:v>Applicant</x:v>
+      </x:c>
+      <x:c r="C15" s="39" t="str">
+        <x:v>Rush Truck Centers</x:v>
+      </x:c>
+      <x:c r="D15" s="39" t="str">
+        <x:v>Jefferson I-85 / Hog Mountain Road</x:v>
+      </x:c>
+      <x:c r="E15" s="39" t="str">
+        <x:v>End user / applicant</x:v>
+      </x:c>
+      <x:c r="F15" s="39" t="str">
+        <x:v>Applicant for conditional LI modification and truck-service use</x:v>
+      </x:c>
+      <x:c r="G15" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
+      </x:c>
+      <x:c r="H15" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="39" t="str">
+        <x:v>JM Business Park IV LLC</x:v>
+      </x:c>
+      <x:c r="B16" s="39" t="str">
+        <x:v>Property owner</x:v>
+      </x:c>
+      <x:c r="C16" s="39" t="str">
+        <x:v>JM Business Park IV LLC</x:v>
+      </x:c>
+      <x:c r="D16" s="39" t="str">
+        <x:v>Jefferson I-85 / Hog Mountain Road</x:v>
+      </x:c>
+      <x:c r="E16" s="39" t="str">
+        <x:v>Landowner</x:v>
+      </x:c>
+      <x:c r="F16" s="39" t="str">
+        <x:v>Named property owner for Rush Truck Centers application</x:v>
+      </x:c>
+      <x:c r="G16" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/CivicAlerts.aspx?AID=77</x:v>
+      </x:c>
+      <x:c r="H16" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="39" t="str">
+        <x:v>RaceTrac Inc.</x:v>
+      </x:c>
+      <x:c r="B17" s="39" t="str">
+        <x:v>Developer / operator</x:v>
+      </x:c>
+      <x:c r="C17" s="39" t="str">
+        <x:v>RaceTrac</x:v>
+      </x:c>
+      <x:c r="D17" s="39" t="str">
+        <x:v>Jefferson I-85 node</x:v>
+      </x:c>
+      <x:c r="E17" s="39" t="str">
+        <x:v>End user / applicant</x:v>
+      </x:c>
+      <x:c r="F17" s="39" t="str">
+        <x:v>Applicant proposing travel-center diesel expansion near I-85</x:v>
+      </x:c>
+      <x:c r="G17" s="39" t="str">
+        <x:v>https://negrc.org/uploads/sites/4/2025/04/DRI4420.RacetracExtendedDieselOffer.Jefferson.FinalReport.pdf</x:v>
+      </x:c>
+      <x:c r="H17" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="39" t="str">
+        <x:v>Dawn Maddox</x:v>
+      </x:c>
+      <x:c r="B18" s="39" t="str">
+        <x:v>Mayor</x:v>
+      </x:c>
+      <x:c r="C18" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D18" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E18" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F18" s="39" t="str">
+        <x:v>Mayor in Jefferson council-manager government</x:v>
+      </x:c>
+      <x:c r="G18" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H18" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="39" t="str">
+        <x:v>Steve Kinney</x:v>
+      </x:c>
+      <x:c r="B19" s="39" t="str">
+        <x:v>Mayor Pro Tempore / District 1 Councilmember</x:v>
+      </x:c>
+      <x:c r="C19" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D19" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E19" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F19" s="39" t="str">
+        <x:v>City Council member</x:v>
+      </x:c>
+      <x:c r="G19" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H19" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="39" t="str">
+        <x:v>Annette Studivant</x:v>
+      </x:c>
+      <x:c r="B20" s="39" t="str">
+        <x:v>District 2 Councilmember</x:v>
+      </x:c>
+      <x:c r="C20" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D20" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E20" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F20" s="39" t="str">
+        <x:v>City Council member</x:v>
+      </x:c>
+      <x:c r="G20" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H20" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="39" t="str">
+        <x:v>Cody Cain</x:v>
+      </x:c>
+      <x:c r="B21" s="39" t="str">
+        <x:v>District 3 Councilmember</x:v>
+      </x:c>
+      <x:c r="C21" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D21" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E21" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F21" s="39" t="str">
+        <x:v>City Council member</x:v>
+      </x:c>
+      <x:c r="G21" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H21" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="39" t="str">
+        <x:v>Mark Mobley</x:v>
+      </x:c>
+      <x:c r="B22" s="39" t="str">
+        <x:v>District 4 Councilmember</x:v>
+      </x:c>
+      <x:c r="C22" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D22" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E22" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F22" s="39" t="str">
+        <x:v>City Council member</x:v>
+      </x:c>
+      <x:c r="G22" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H22" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="39" t="str">
+        <x:v>Alex Crawford</x:v>
+      </x:c>
+      <x:c r="B23" s="39" t="str">
+        <x:v>District 5 Councilmember</x:v>
+      </x:c>
+      <x:c r="C23" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D23" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E23" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F23" s="39" t="str">
+        <x:v>City Council member</x:v>
+      </x:c>
+      <x:c r="G23" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/286/City-Council</x:v>
+      </x:c>
+      <x:c r="H23" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="39" t="str">
+        <x:v>Rob Alexander</x:v>
+      </x:c>
+      <x:c r="B24" s="39" t="str">
+        <x:v>City Attorney</x:v>
+      </x:c>
+      <x:c r="C24" s="39" t="str">
+        <x:v>Davidson Hopkins and Alexander</x:v>
+      </x:c>
+      <x:c r="D24" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E24" s="39" t="str">
+        <x:v>Public counsel</x:v>
+      </x:c>
+      <x:c r="F24" s="39" t="str">
+        <x:v>Listed official City Attorney</x:v>
+      </x:c>
+      <x:c r="G24" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/m/directory</x:v>
+      </x:c>
+      <x:c r="H24" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="39" t="str">
+        <x:v>Priscilla Murphy</x:v>
+      </x:c>
+      <x:c r="B25" s="39" t="str">
+        <x:v>City Manager</x:v>
+      </x:c>
+      <x:c r="C25" s="39" t="str">
+        <x:v>City of Jefferson</x:v>
+      </x:c>
+      <x:c r="D25" s="39" t="str">
+        <x:v>Jefferson</x:v>
+      </x:c>
+      <x:c r="E25" s="39" t="str">
+        <x:v>Senior staff</x:v>
+      </x:c>
+      <x:c r="F25" s="39" t="str">
+        <x:v>Listed official City Manager</x:v>
+      </x:c>
+      <x:c r="G25" s="39" t="str">
+        <x:v>https://www.jeffersonga.gov/m/directory</x:v>
+      </x:c>
+      <x:c r="H25" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="39" t="str">
+        <x:v>Trammell Crow Company</x:v>
+      </x:c>
+      <x:c r="B26" s="39" t="str">
+        <x:v>Developer</x:v>
+      </x:c>
+      <x:c r="C26" s="39" t="str">
+        <x:v>Trammell Crow Company</x:v>
+      </x:c>
+      <x:c r="D26" s="39" t="str">
+        <x:v>Jackson 85 North</x:v>
+      </x:c>
+      <x:c r="E26" s="39" t="str">
+        <x:v>Developer</x:v>
+      </x:c>
+      <x:c r="F26" s="39" t="str">
+        <x:v>Developer of completed Pendergrass Class-A warehouse park</x:v>
+      </x:c>
+      <x:c r="G26" s="39" t="str">
+        <x:v>http://www.trammellcrow.com/projects/jackson-85-north</x:v>
+      </x:c>
+      <x:c r="H26" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="39" t="str">
+        <x:v>CBRE Investment Management</x:v>
+      </x:c>
+      <x:c r="B27" s="39" t="str">
+        <x:v>Capital partner</x:v>
+      </x:c>
+      <x:c r="C27" s="39" t="str">
+        <x:v>CBRE Investment Management</x:v>
+      </x:c>
+      <x:c r="D27" s="39" t="str">
+        <x:v>Jackson 85 North</x:v>
+      </x:c>
+      <x:c r="E27" s="39" t="str">
+        <x:v>Capital partner</x:v>
+      </x:c>
+      <x:c r="F27" s="39" t="str">
+        <x:v>Joint venture partner reported for Jackson 85 North phase one</x:v>
+      </x:c>
+      <x:c r="G27" s="39" t="str">
+        <x:v>https://rebusinessonline.com/category/georgia/page/29/</x:v>
+      </x:c>
+      <x:c r="H27" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="39" t="str">
+        <x:v>Evans</x:v>
+      </x:c>
+      <x:c r="B28" s="39" t="str">
+        <x:v>General contractor</x:v>
+      </x:c>
+      <x:c r="C28" s="39" t="str">
+        <x:v>Evans General Contractors</x:v>
+      </x:c>
+      <x:c r="D28" s="39" t="str">
+        <x:v>Jackson 85 North phase two</x:v>
+      </x:c>
+      <x:c r="E28" s="39" t="str">
+        <x:v>General contractor</x:v>
+      </x:c>
+      <x:c r="F28" s="39" t="str">
+        <x:v>Reported design-build general contractor for phase two</x:v>
+      </x:c>
+      <x:c r="G28" s="39" t="str">
+        <x:v>https://rebusinessonline.com/category/georgia/page/29/</x:v>
+      </x:c>
+      <x:c r="H28" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="39" t="str">
+        <x:v>Stephanie Harris</x:v>
+      </x:c>
+      <x:c r="B29" s="39" t="str">
+        <x:v>Senior Development Manager</x:v>
+      </x:c>
+      <x:c r="C29" s="39" t="str">
+        <x:v>Trammell Crow Company</x:v>
+      </x:c>
+      <x:c r="D29" s="39" t="str">
+        <x:v>Jackson 85 North</x:v>
+      </x:c>
+      <x:c r="E29" s="39" t="str">
+        <x:v>Developer representative</x:v>
+      </x:c>
+      <x:c r="F29" s="39" t="str">
+        <x:v>Listed project contact</x:v>
+      </x:c>
+      <x:c r="G29" s="39" t="str">
+        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
+      </x:c>
+      <x:c r="H29" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="39" t="str">
+        <x:v>Drew Fredrick</x:v>
+      </x:c>
+      <x:c r="B30" s="39" t="str">
+        <x:v>Executive Vice President</x:v>
+      </x:c>
+      <x:c r="C30" s="39" t="str">
+        <x:v>Trammell Crow Company</x:v>
+      </x:c>
+      <x:c r="D30" s="39" t="str">
+        <x:v>Jackson 85 North</x:v>
+      </x:c>
+      <x:c r="E30" s="39" t="str">
+        <x:v>Developer representative</x:v>
+      </x:c>
+      <x:c r="F30" s="39" t="str">
+        <x:v>Listed project contact</x:v>
+      </x:c>
+      <x:c r="G30" s="39" t="str">
+        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
+      </x:c>
+      <x:c r="H30" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="39" t="str">
+        <x:v>Tyler Cooksey</x:v>
+      </x:c>
+      <x:c r="B31" s="39" t="str">
+        <x:v>Senior Vice President</x:v>
+      </x:c>
+      <x:c r="C31" s="39" t="str">
+        <x:v>Trammell Crow Company</x:v>
+      </x:c>
+      <x:c r="D31" s="39" t="str">
+        <x:v>Jackson 85 North</x:v>
+      </x:c>
+      <x:c r="E31" s="39" t="str">
+        <x:v>Developer representative</x:v>
+      </x:c>
+      <x:c r="F31" s="39" t="str">
+        <x:v>Listed project contact</x:v>
+      </x:c>
+      <x:c r="G31" s="39" t="str">
+        <x:v>https://www.trammellcrow.com/projects/jackson-85-north</x:v>
+      </x:c>
+      <x:c r="H31" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="39" t="str">
+        <x:v>Bill Ellis</x:v>
+      </x:c>
+      <x:c r="B32" s="39" t="str">
+        <x:v>Mayor</x:v>
+      </x:c>
+      <x:c r="C32" s="39" t="str">
+        <x:v>City of Pendergrass</x:v>
+      </x:c>
+      <x:c r="D32" s="39" t="str">
+        <x:v>Pendergrass</x:v>
+      </x:c>
+      <x:c r="E32" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F32" s="39" t="str">
+        <x:v>Mayor in strong-mayor government</x:v>
+      </x:c>
+      <x:c r="G32" s="39" t="str">
+        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
+      </x:c>
+      <x:c r="H32" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="39" t="str">
+        <x:v>Gabriel Gomez</x:v>
+      </x:c>
+      <x:c r="B33" s="39" t="str">
+        <x:v>Mayor Pro Tem / Councilmember</x:v>
+      </x:c>
+      <x:c r="C33" s="39" t="str">
+        <x:v>City of Pendergrass</x:v>
+      </x:c>
+      <x:c r="D33" s="39" t="str">
+        <x:v>Pendergrass</x:v>
+      </x:c>
+      <x:c r="E33" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F33" s="39" t="str">
+        <x:v>Current councilmember and Mayor Pro Tem</x:v>
+      </x:c>
+      <x:c r="G33" s="39" t="str">
+        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
+      </x:c>
+      <x:c r="H33" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="39" t="str">
+        <x:v>Laura Bigley</x:v>
+      </x:c>
+      <x:c r="B34" s="39" t="str">
+        <x:v>Councilmember</x:v>
+      </x:c>
+      <x:c r="C34" s="39" t="str">
+        <x:v>City of Pendergrass</x:v>
+      </x:c>
+      <x:c r="D34" s="39" t="str">
+        <x:v>Pendergrass</x:v>
+      </x:c>
+      <x:c r="E34" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F34" s="39" t="str">
+        <x:v>Current councilmember</x:v>
+      </x:c>
+      <x:c r="G34" s="39" t="str">
+        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
+      </x:c>
+      <x:c r="H34" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="39" t="str">
+        <x:v>Bob Carter</x:v>
+      </x:c>
+      <x:c r="B35" s="39" t="str">
+        <x:v>Councilmember</x:v>
+      </x:c>
+      <x:c r="C35" s="39" t="str">
+        <x:v>City of Pendergrass</x:v>
+      </x:c>
+      <x:c r="D35" s="39" t="str">
+        <x:v>Pendergrass</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F35" s="39" t="str">
+        <x:v>Current councilmember</x:v>
+      </x:c>
+      <x:c r="G35" s="39" t="str">
+        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
+      </x:c>
+      <x:c r="H35" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="39" t="str">
+        <x:v>Sylvia Basak</x:v>
+      </x:c>
+      <x:c r="B36" s="39" t="str">
+        <x:v>Councilmember</x:v>
+      </x:c>
+      <x:c r="C36" s="39" t="str">
+        <x:v>City of Pendergrass</x:v>
+      </x:c>
+      <x:c r="D36" s="39" t="str">
+        <x:v>Pendergrass</x:v>
+      </x:c>
+      <x:c r="E36" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F36" s="39" t="str">
+        <x:v>Current councilmember</x:v>
+      </x:c>
+      <x:c r="G36" s="39" t="str">
+        <x:v>https://cityofpendergrass.net/mayor-and-council/</x:v>
+      </x:c>
+      <x:c r="H36" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="39" t="str">
+        <x:v>Dr. J. Clark Hill III</x:v>
+      </x:c>
+      <x:c r="B37" s="39" t="str">
+        <x:v>Mayor</x:v>
+      </x:c>
+      <x:c r="C37" s="39" t="str">
+        <x:v>City of Commerce</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="str">
+        <x:v>Commerce</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F37" s="39" t="str">
+        <x:v>Mayor and chief executive officer</x:v>
+      </x:c>
+      <x:c r="G37" s="39" t="str">
+        <x:v>https://www.commercega.gov/government/elected-officials</x:v>
+      </x:c>
+      <x:c r="H37" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="39" t="str">
+        <x:v>Keith Burchett</x:v>
+      </x:c>
+      <x:c r="B38" s="39" t="str">
+        <x:v>Mayor Pro Tem</x:v>
+      </x:c>
+      <x:c r="C38" s="39" t="str">
+        <x:v>City of Commerce</x:v>
+      </x:c>
+      <x:c r="D38" s="39" t="str">
+        <x:v>Commerce</x:v>
+      </x:c>
+      <x:c r="E38" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F38" s="39" t="str">
+        <x:v>Mayor Pro Tem</x:v>
+      </x:c>
+      <x:c r="G38" s="39" t="str">
+        <x:v>https://www.commercega.gov/government/elected-officials</x:v>
+      </x:c>
+      <x:c r="H38" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="39" t="str">
+        <x:v>Matthew Hailey</x:v>
+      </x:c>
+      <x:c r="B39" s="39" t="str">
+        <x:v>City Manager</x:v>
+      </x:c>
+      <x:c r="C39" s="39" t="str">
+        <x:v>City of Commerce</x:v>
+      </x:c>
+      <x:c r="D39" s="39" t="str">
+        <x:v>Commerce</x:v>
+      </x:c>
+      <x:c r="E39" s="39" t="str">
+        <x:v>Senior staff</x:v>
+      </x:c>
+      <x:c r="F39" s="39" t="str">
+        <x:v>Listed official City Manager</x:v>
+      </x:c>
+      <x:c r="G39" s="39" t="str">
+        <x:v>https://commercega.gov/government</x:v>
+      </x:c>
+      <x:c r="H39" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="39" t="str">
+        <x:v>Leland Smith</x:v>
+      </x:c>
+      <x:c r="B40" s="39" t="str">
+        <x:v>Planning and Zoning Administrator</x:v>
+      </x:c>
+      <x:c r="C40" s="39" t="str">
+        <x:v>City of Commerce</x:v>
+      </x:c>
+      <x:c r="D40" s="39" t="str">
+        <x:v>Taylor &amp; Mathis Commerce case</x:v>
+      </x:c>
+      <x:c r="E40" s="39" t="str">
+        <x:v>Staff gatekeeper</x:v>
+      </x:c>
+      <x:c r="F40" s="39" t="str">
+        <x:v>Presented annexation rezoning and conditional use to Planning Commission and City Council</x:v>
+      </x:c>
+      <x:c r="G40" s="39" t="str">
+        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
+      </x:c>
+      <x:c r="H40" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="39" t="str">
+        <x:v>Dillon Anthony</x:v>
+      </x:c>
+      <x:c r="B41" s="39" t="str">
+        <x:v>Planning and Development Superintendent / Building Inspector</x:v>
+      </x:c>
+      <x:c r="C41" s="39" t="str">
+        <x:v>City of Commerce</x:v>
+      </x:c>
+      <x:c r="D41" s="39" t="str">
+        <x:v>Taylor &amp; Mathis Commerce case</x:v>
+      </x:c>
+      <x:c r="E41" s="39" t="str">
+        <x:v>Staff gatekeeper</x:v>
+      </x:c>
+      <x:c r="F41" s="39" t="str">
+        <x:v>Requested/presented Taylor &amp; Mathis agenda items and clarified acreage/parcel details</x:v>
+      </x:c>
+      <x:c r="G41" s="39" t="str">
+        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
+      </x:c>
+      <x:c r="H41" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="39" t="str">
+        <x:v>Taylor &amp; Mathis Inc.</x:v>
+      </x:c>
+      <x:c r="B42" s="39" t="str">
+        <x:v>Applicant</x:v>
+      </x:c>
+      <x:c r="C42" s="39" t="str">
+        <x:v>Taylor &amp; Mathis Inc.</x:v>
+      </x:c>
+      <x:c r="D42" s="39" t="str">
+        <x:v>Commerce distribution center / truck terminal</x:v>
+      </x:c>
+      <x:c r="E42" s="39" t="str">
+        <x:v>Developer/applicant</x:v>
+      </x:c>
+      <x:c r="F42" s="39" t="str">
+        <x:v>Applicant for annexation rezoning and conditional use for 121.373-acre distribution center with truck terminals and warehouse/storage</x:v>
+      </x:c>
+      <x:c r="G42" s="39" t="str">
+        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
+      </x:c>
+      <x:c r="H42" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="39" t="str">
+        <x:v>Mahaffey Pickens Tucker LLP</x:v>
+      </x:c>
+      <x:c r="B43" s="39" t="str">
+        <x:v>Zoning counsel/applicant representative</x:v>
+      </x:c>
+      <x:c r="C43" s="39" t="str">
+        <x:v>Mahaffey Pickens Tucker LLP</x:v>
+      </x:c>
+      <x:c r="D43" s="39" t="str">
+        <x:v>Commerce distribution center / truck terminal</x:v>
+      </x:c>
+      <x:c r="E43" s="39" t="str">
+        <x:v>Zoning counsel</x:v>
+      </x:c>
+      <x:c r="F43" s="39" t="str">
+        <x:v>Listed as c/o applicant representative for Taylor &amp; Mathis Commerce cases</x:v>
+      </x:c>
+      <x:c r="G43" s="39" t="str">
+        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
+      </x:c>
+      <x:c r="H43" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="39" t="str">
+        <x:v>Anthony L. Wood Jr. and Benjamin A. Wood</x:v>
+      </x:c>
+      <x:c r="B44" s="39" t="str">
+        <x:v>Property owners</x:v>
+      </x:c>
+      <x:c r="C44" s="39" t="str">
+        <x:v>Private owners</x:v>
+      </x:c>
+      <x:c r="D44" s="39" t="str">
+        <x:v>Commerce distribution center / truck terminal</x:v>
+      </x:c>
+      <x:c r="E44" s="39" t="str">
+        <x:v>Landowner</x:v>
+      </x:c>
+      <x:c r="F44" s="39" t="str">
+        <x:v>Listed as property owners for parcels 020 002 and 020 008</x:v>
+      </x:c>
+      <x:c r="G44" s="39" t="str">
+        <x:v>https://commercega.granicus.com/MinutesViewer.php?view_id=1&amp;clip_id=409&amp;doc_id=7aa825a7-6685-11f0-b7f5-005056a89546</x:v>
+      </x:c>
+      <x:c r="H44" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="39" t="str">
+        <x:v>Debbie Martin</x:v>
+      </x:c>
+      <x:c r="B45" s="39" t="str">
+        <x:v>Mayor</x:v>
+      </x:c>
+      <x:c r="C45" s="39" t="str">
+        <x:v>City of Hoschton</x:v>
+      </x:c>
+      <x:c r="D45" s="39" t="str">
+        <x:v>Hoschton</x:v>
+      </x:c>
+      <x:c r="E45" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F45" s="39" t="str">
+        <x:v>Current Mayor</x:v>
+      </x:c>
+      <x:c r="G45" s="39" t="str">
+        <x:v>https://www.cityofhoschton.net/directory-listing/mariya-bentz</x:v>
+      </x:c>
+      <x:c r="H45" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="39" t="str">
+        <x:v>Kurt Ward</x:v>
+      </x:c>
+      <x:c r="B46" s="39" t="str">
+        <x:v>Mayor</x:v>
+      </x:c>
+      <x:c r="C46" s="39" t="str">
+        <x:v>Town of Braselton</x:v>
+      </x:c>
+      <x:c r="D46" s="39" t="str">
+        <x:v>Braselton Jackson County area</x:v>
+      </x:c>
+      <x:c r="E46" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F46" s="39" t="str">
+        <x:v>Mayor and voting member of Town Council</x:v>
+      </x:c>
+      <x:c r="G46" s="39" t="str">
+        <x:v>https://www.braseltonmayor.org/town-council</x:v>
+      </x:c>
+      <x:c r="H46" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="39" t="str">
+        <x:v>Becky Richardson</x:v>
+      </x:c>
+      <x:c r="B47" s="39" t="str">
+        <x:v>District 1 Councilmember / Mayor Pro Tem</x:v>
+      </x:c>
+      <x:c r="C47" s="39" t="str">
+        <x:v>Town of Braselton</x:v>
+      </x:c>
+      <x:c r="D47" s="39" t="str">
+        <x:v>Braselton Jackson County area</x:v>
+      </x:c>
+      <x:c r="E47" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F47" s="39" t="str">
+        <x:v>Listed Town Council member</x:v>
+      </x:c>
+      <x:c r="G47" s="39" t="str">
+        <x:v>https://www.braseltonmayor.org/town-council</x:v>
+      </x:c>
+      <x:c r="H47" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="39" t="str">
+        <x:v>Richard Harper</x:v>
+      </x:c>
+      <x:c r="B48" s="39" t="str">
+        <x:v>District 2 Councilmember</x:v>
+      </x:c>
+      <x:c r="C48" s="39" t="str">
+        <x:v>Town of Braselton</x:v>
+      </x:c>
+      <x:c r="D48" s="39" t="str">
+        <x:v>Braselton Jackson County area</x:v>
+      </x:c>
+      <x:c r="E48" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F48" s="39" t="str">
+        <x:v>Listed Town Council member</x:v>
+      </x:c>
+      <x:c r="G48" s="39" t="str">
+        <x:v>https://www.braseltonmayor.org/town-council</x:v>
+      </x:c>
+      <x:c r="H48" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="39" t="str">
+        <x:v>Tom Logan</x:v>
+      </x:c>
+      <x:c r="B49" s="39" t="str">
+        <x:v>District 3 Councilmember</x:v>
+      </x:c>
+      <x:c r="C49" s="39" t="str">
+        <x:v>Town of Braselton</x:v>
+      </x:c>
+      <x:c r="D49" s="39" t="str">
+        <x:v>Braselton Jackson County area</x:v>
+      </x:c>
+      <x:c r="E49" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F49" s="39" t="str">
+        <x:v>Listed Town Council member</x:v>
+      </x:c>
+      <x:c r="G49" s="39" t="str">
+        <x:v>https://www.braseltonmayor.org/town-council</x:v>
+      </x:c>
+      <x:c r="H49" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="39" t="str">
+        <x:v>James Murphy</x:v>
+      </x:c>
+      <x:c r="B50" s="39" t="str">
+        <x:v>District 4 Councilmember</x:v>
+      </x:c>
+      <x:c r="C50" s="39" t="str">
+        <x:v>Town of Braselton</x:v>
+      </x:c>
+      <x:c r="D50" s="39" t="str">
+        <x:v>Braselton Jackson County area</x:v>
+      </x:c>
+      <x:c r="E50" s="39" t="str">
+        <x:v>Current decision-maker</x:v>
+      </x:c>
+      <x:c r="F50" s="39" t="str">
+        <x:v>Listed Town Council member</x:v>
+      </x:c>
+      <x:c r="G50" s="39" t="str">
+        <x:v>https://www.braseltonmayor.org/town-council</x:v>
+      </x:c>
+      <x:c r="H50" s="39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
